--- a/CaseAnalysis.xlsx
+++ b/CaseAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ΜΤΠΤΧ\AIDL_B_02 - Advanced Topics in Deep Learning\Waldiez\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thodorischaros/Documents/MSc/AIDL_B02_AdvancedTopicsInDeepLearning/assignments/Agentic-AI-Detective-Agency-using-Waldiez/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D3490A-6ED7-4325-8A32-A647D24AD590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BECCDDE-37AE-2A4F-9BFF-08E4AEAEAFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38265" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{2417D041-2CBB-4EA8-882E-D9B941780DCB}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" activeTab="1" xr2:uid="{2417D041-2CBB-4EA8-882E-D9B941780DCB}"/>
   </bookViews>
   <sheets>
     <sheet name="CaseStatistics" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
   <si>
     <t>case_id</t>
   </si>
@@ -174,25 +173,56 @@
     <t>persistent_fails (the below questions were failed across all runs of each case)</t>
   </si>
   <si>
-    <t xml:space="preserve">The agents tried to interpret clues that contained "if and only if" like "Monsieur Brunette was in the Carriage House at 12:30 AM if and only if the suspect motivated by Hatred was in the Gazebo at 12:15 AM"
-which was the connection between Monsieur Brunette and Hatred. This can be seen in the logs, for example Monsieur Brunette: Carriage House (if suspect motivated by Hatred is in Gazebo) but </t>
-  </si>
-  <si>
-    <t>The most important clue is: "The murderer moved from the Fountain to the Gazebo at 11:15 PM" which means that the murder occurred @11.00 PM and @Fountain.
+    <t>In Run 1 the Auditor succesfully re-validated the answer from the detective and updated the murderer from Professor Plum to Monsieur Brunette. This happened to other runs also.</t>
+  </si>
+  <si>
+    <t>The Auditor failed to correct the murderer and the motive chosen from the Detective. It updated them with wrong answers also. The same applies for the Motive also, Pride --&gt; Betrayal.</t>
+  </si>
+  <si>
+    <t>The Auditor succesfully found a Physical Violation to rule out a murderer (Sgt. Gray) but chose wrong murderer again (Mrs. Peacock)</t>
+  </si>
+  <si>
+    <t>The Auditor did not challenge the answers from the Detective but just "verified" the physical feasibility and not the logical.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question E
+The clues
+"The suspect motivated by Power was in the same room as the Candlestick at 11:45 PM" and 
+"The Poison was in the Kitchen at 12:00 AM if and only if the suspect motivated by Power was in the Billiard Room at 12:00 AM."
+The agents failed to follow both paths of bidirectional clues and as a result select the wrong path and fail to verify the movement of the "Power" from 11:45 to 12:00 </t>
+  </si>
+  <si>
+    <t>Questions C,D
+The most important clue is: "The murderer moved from the Fountain to the Gazebo at 11:15 PM" which means that the murder occurred @11.00 PM and @Fountain.
 Since the agents failed to base the solution on this they always missed questions C and D.</t>
   </si>
   <si>
-    <t>In Run 1 the Auditor succesfully re-validated the answer from the detective and updated the murderer from Professor Plum to Monsieur Brunette. This happened to other runs also.</t>
-  </si>
-  <si>
-    <t>The Auditor failed to correct the murderer and the motive chosen from the Detective. It updated them with wrong answers also. The same applies for the Motive also, Pride --&gt; Betrayal.</t>
-  </si>
-  <si>
-    <t>The Auditor succesfully found a Physical Violation to rule out a murderer (Sgt. Gray) but chose wrong murderer again (Mrs. Peacock)</t>
-  </si>
-  <si>
-    <t>The agents failed to combine these clues "The murderer moved the Wrench from the Cloak Room to the Hall at 12:30 AM." and
-"The suspect motivated by Hatred was in the Cloak Room at 11:30 PM" to identify the motive and based on that find the murderer.</t>
+    <t>Question E
+The agents tried to interpret clues that contained "if and only if" like "Monsieur Brunette was in the Carriage House at 12:30 AM if and only if the suspect motivated by Hatred was in the Gazebo at 12:15 AM"
+which was the connection between Monsieur Brunette and Hatred. This can be seen in the logs, for example Monsieur Brunette: Carriage House (if suspect motivated by Hatred is in Gazebo) but failed to follow 
+the correct path.</t>
+  </si>
+  <si>
+    <t>Questions A,D
+The agents failed to combine these clues
+"The murderer moved the Wrench from the Cloak Room to the Hall at 12:30 AM."
+"The suspect motivated by Hatred was in the Cloak Room at 11:30 PM"
+to identify the motive "Hatred" and based on that find the murderer.</t>
+  </si>
+  <si>
+    <t>Question D
+The motive "Fear" was never exclicitly referenced at a clue, so the agents had to deduce the rest motives in order to find it.</t>
+  </si>
+  <si>
+    <t>Question A
+The agents failed to combine these clues in order to connect Mrs White with the Fountain:
+"Mrs. White and the Wrench were at the Fountain together at least once."
+"The murderer and Mr. Boddy were at the Fountain together at least once" 
+"The murderer was at the Fountain at 12:00 AM."</t>
+  </si>
+  <si>
+    <t>Question F
+The agents had problem following both paths of clue "The suspect motivated by Jealousy was in the Billiard Room at 11:45 PM or the suspect motivated by Hatred was in the Kitchen at 11:45 PM."</t>
   </si>
 </sst>
 </file>
@@ -561,17 +591,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3748830A-B28B-4F54-9596-6D91485AA2CB}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +621,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1052</v>
       </c>
@@ -611,7 +641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1182</v>
       </c>
@@ -631,7 +661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1230</v>
       </c>
@@ -651,7 +681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2145</v>
       </c>
@@ -671,7 +701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2176</v>
       </c>
@@ -691,7 +721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2279</v>
       </c>
@@ -711,7 +741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2372</v>
       </c>
@@ -731,7 +761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2680</v>
       </c>
@@ -751,7 +781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2799</v>
       </c>
@@ -771,7 +801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>2973</v>
       </c>
@@ -798,14 +828,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6E4106-5CC9-44AD-AC20-27CF18A53C82}">
-  <dimension ref="A1:B71"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="191.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="158.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -813,7 +843,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1052</v>
       </c>
@@ -821,42 +851,42 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="80" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>1182</v>
       </c>
@@ -864,37 +894,37 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="80" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>1230</v>
       </c>
@@ -902,175 +932,200 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="80" x14ac:dyDescent="0.2">
+      <c r="B24" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="B25" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="80" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="32" x14ac:dyDescent="0.2">
+      <c r="B27" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>2145</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B30" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>2176</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="1"/>
+      <c r="B40" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B39" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
         <v>2279</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B47" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
+      <c r="B48" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
         <v>2372</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B54" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="1"/>
+      <c r="B55" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" s="1"/>
+      <c r="B56" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B54" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
         <v>2680</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B62" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" s="1"/>
+      <c r="B63" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" s="1"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
         <v>2799</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B67" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" t="s">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" s="1"/>
+      <c r="B68" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
         <v>2973</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B72" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
-      <c r="B70" t="s">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" s="1"/>
+      <c r="B73" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B74" t="s">
         <v>32</v>
       </c>
     </row>

--- a/CaseAnalysis.xlsx
+++ b/CaseAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thodorischaros/Documents/MSc/AIDL_B02_AdvancedTopicsInDeepLearning/assignments/Agentic-AI-Detective-Agency-using-Waldiez/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ΜΤΠΤΧ\AIDL_B_02 - Advanced Topics in Deep Learning\Waldiez\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BECCDDE-37AE-2A4F-9BFF-08E4AEAEAFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84938DB3-3B37-4E9C-B4BA-5CAA54F34C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16820" activeTab="1" xr2:uid="{2417D041-2CBB-4EA8-882E-D9B941780DCB}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{2417D041-2CBB-4EA8-882E-D9B941780DCB}"/>
   </bookViews>
   <sheets>
     <sheet name="CaseStatistics" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
   <si>
     <t>case_id</t>
   </si>
@@ -101,45 +101,12 @@
     <t>4/6</t>
   </si>
   <si>
-    <t>D. TIME</t>
-  </si>
-  <si>
     <t>C. WHERE</t>
   </si>
   <si>
-    <t>E. MOTIVE</t>
-  </si>
-  <si>
-    <t>A. WHO</t>
-  </si>
-  <si>
-    <t>D. MOTIVE</t>
-  </si>
-  <si>
-    <t>E. CANDLESTICK LOCATION</t>
-  </si>
-  <si>
-    <t>F. JEALOUSLY WHO</t>
-  </si>
-  <si>
-    <t>C. TIME</t>
-  </si>
-  <si>
-    <t>B. WEAPON</t>
-  </si>
-  <si>
-    <t>F. MONSIEUR BRUNETTE LOCATION</t>
-  </si>
-  <si>
-    <t>H. MRS WHITE @11.00 PM LOCATION</t>
-  </si>
-  <si>
     <t>F. MR GREEN @11.00 PM LOCATION</t>
   </si>
   <si>
-    <t>F. BETRAYAL LOCATION</t>
-  </si>
-  <si>
     <t>{'A': 'Monsieur Brunette', 'B': 'Knife', 'C': 'Fountain', 'D': '11:00 PM', 'E': 'Hatred', 'F': 'Ballroom', 'G': 'Ballroom'}</t>
   </si>
   <si>
@@ -176,60 +143,529 @@
     <t>In Run 1 the Auditor succesfully re-validated the answer from the detective and updated the murderer from Professor Plum to Monsieur Brunette. This happened to other runs also.</t>
   </si>
   <si>
-    <t>The Auditor failed to correct the murderer and the motive chosen from the Detective. It updated them with wrong answers also. The same applies for the Motive also, Pride --&gt; Betrayal.</t>
-  </si>
-  <si>
     <t>The Auditor succesfully found a Physical Violation to rule out a murderer (Sgt. Gray) but chose wrong murderer again (Mrs. Peacock)</t>
   </si>
   <si>
     <t>The Auditor did not challenge the answers from the Detective but just "verified" the physical feasibility and not the logical.</t>
   </si>
   <si>
-    <t xml:space="preserve">Question E
+    <t>The Auditor updated tried to update the answers from Detective but with wrong answers. He failed to correct the murderer and the motive chosen from the Detective (Sgt. Gray --&gt; MRs Peacock on run 4). The same applies for the Motive also, Pride --&gt; Betrayal.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Question A (WHO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The agents failed to combine these clues in order to connect Mrs White with the Fountain:
+"Mrs. White and the Wrench were at the Fountain together at least once."
+"The murderer and Mr. Boddy were at the Fountain together at least once" 
+"The murderer was at the Fountain at 12:00 AM."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Question D (MOTIVE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The motive "Fear" was never exclicitly referenced at a clue, so the agents had to deduce the rest motives in order to find it.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Question F (JEALOUSLY WHO)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The agents had problem following both paths of clue "The suspect motivated by Jealousy was in the Billiard Room at 11:45 PM or the suspect motivated by Hatred was in the Kitchen at 11:45 PM."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Questions C (WHERE), D (TIME)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The most important clue is: "The murderer moved from the Fountain to the Gazebo at 11:15 PM" which means that the murder occurred @11.00 PM and @Fountain.
+Since the agents failed to base the solution on this they always missed questions C and D.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Question E (MOTIVE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The agents tried to interpret clues that contained "if and only if" like "Monsieur Brunette was in the Carriage House at 12:30 AM if and only if the suspect motivated by Hatred was in the Gazebo at 12:15 AM"
+which was the connection between Monsieur Brunette and Hatred. This can be seen in the logs, for example Monsieur Brunette: Carriage House (if suspect motivated by Hatred is in Gazebo) but failed to follow 
+the correct path.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Questions A (WHO), D (MOTIVE)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+The agents failed to combine these clues
+"The murderer moved the Wrench from the Cloak Room to the Hall at 12:30 AM."
+"The suspect motivated by Hatred was in the Cloak Room at 11:30 PM"
+to identify the motive "Hatred" and based on that find the murderer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Questions C (WHERE), D (TIME)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The agents failed to locate the location of Miss Scarlet by combining the map from Forensics and these clues "Madame Rose moved from the Library to the Conservatory at 10:00 PM" and "Miss Scarlet was in the room just east of Madame Rose at 11:00 PM" in order find the murder PLACE and TIME.
+The real problem comes from the problem to process and follow correctly both paths of "The murderer was in the Dining Room at 11:00 PM if and only if the Horseshoe was in the Lounge at 09:00 PM".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question E (MOTIVE)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The agents only chose Hatred and Power.
+The agents failed to follow both paths of "The suspect motivated by Fear was in the Lounge at 09:00 PM if and only if Sgt. Gray was in the Dining Room at 12:00 AM"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Question E (CANDLESTICK LOCATION @12:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 The clues
 "The suspect motivated by Power was in the same room as the Candlestick at 11:45 PM" and 
 "The Poison was in the Kitchen at 12:00 AM if and only if the suspect motivated by Power was in the Billiard Room at 12:00 AM."
 The agents failed to follow both paths of bidirectional clues and as a result select the wrong path and fail to verify the movement of the "Power" from 11:45 to 12:00 </t>
-  </si>
-  <si>
-    <t>Questions C,D
-The most important clue is: "The murderer moved from the Fountain to the Gazebo at 11:15 PM" which means that the murder occurred @11.00 PM and @Fountain.
-Since the agents failed to base the solution on this they always missed questions C and D.</t>
-  </si>
-  <si>
-    <t>Question E
-The agents tried to interpret clues that contained "if and only if" like "Monsieur Brunette was in the Carriage House at 12:30 AM if and only if the suspect motivated by Hatred was in the Gazebo at 12:15 AM"
-which was the connection between Monsieur Brunette and Hatred. This can be seen in the logs, for example Monsieur Brunette: Carriage House (if suspect motivated by Hatred is in Gazebo) but failed to follow 
-the correct path.</t>
-  </si>
-  <si>
-    <t>Questions A,D
-The agents failed to combine these clues
-"The murderer moved the Wrench from the Cloak Room to the Hall at 12:30 AM."
-"The suspect motivated by Hatred was in the Cloak Room at 11:30 PM"
-to identify the motive "Hatred" and based on that find the murderer.</t>
-  </si>
-  <si>
-    <t>Question D
-The motive "Fear" was never exclicitly referenced at a clue, so the agents had to deduce the rest motives in order to find it.</t>
-  </si>
-  <si>
-    <t>Question A
-The agents failed to combine these clues in order to connect Mrs White with the Fountain:
-"Mrs. White and the Wrench were at the Fountain together at least once."
-"The murderer and Mr. Boddy were at the Fountain together at least once" 
-"The murderer was at the Fountain at 12:00 AM."</t>
-  </si>
-  <si>
-    <t>Question F
-The agents had problem following both paths of clue "The suspect motivated by Jealousy was in the Billiard Room at 11:45 PM or the suspect motivated by Hatred was in the Kitchen at 11:45 PM."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question A (WHO), D (MOTIVE)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The agents failed to follow both paths of "Miss Peach was at the Fountain at 12:00 AM if and only if the suspect motivated by Power was in the Drawing Room at 11:45 PM".</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Despite the fact that the agents paired Madame Rose-Power </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(on run 3 "Madame Rose is motivated by Power") </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>they failed to use the json map effectively and place Madame Rose in the Drawing Room. After that they couldnt follow the clues to find Miss Peach is the MURDERER.
+Pride wasn't explicitly named in the clues, so the agents had to eliminate all other 9 motives.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question C (TIME)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In all runs the agents chose 12:00.
+A possible reason might be the fact that all the clues that involved movement occurred at 12:00, so the agents became biased by that.</t>
+    </r>
+  </si>
+  <si>
+    <t>General Comments</t>
+  </si>
+  <si>
+    <t>In some cases the Auditor seems to just pass the Detectives' answer without reasoning</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question F (BETRAYAL LOCATION @12:00)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>This required to eliminate all other motives, as it wasn't referenced at the clues.
+Since the agents failed at pairing Hatred and Power, they failed on this too.</t>
+    </r>
+  </si>
+  <si>
+    <t>On run 4 the agents halucinated and answered an extra question (G).
+They Auditor tried to correct the answers from Detective.
+On run 2 the Auditor wrote "PHYSICAL VIOLATION DETECTED" but instead of declining the solution path the Detective chose and track back the correct, he just changed the suspect to a wrong one.
+On run 5 the MURDERER-ROOM-MOTIVE-extra questions but with wrong answers.</t>
+  </si>
+  <si>
+    <r>
+      <t>On run 10, which was the best score 3/7, both Detective and Auditor provided a solution with 2 correct answers and E,F,G with N/A despite the instructions to always have an answer. The final score was achieved by an</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> intervention of the Archivist</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> who, despite his instructions to just save the final answer, he updated the N/A answers with actual room names one of which was correct.</t>
+    </r>
+  </si>
+  <si>
+    <t>In many cases Qwen model proves to be "small" for this task, with limited reasoning capabilities in comparison with more powerfull models</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question D (MOTIVE)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The agents failed to lock on the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EXPLICITLY mentioned motive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the clue "Mrs. White is motivated by Pride". A possible reason might be the fact that other motives are mentioned more in the clues.
+This could be an easy win since Mrs White was correclty identified as the murderer.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question B (WEAPON)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The problem to identify the weapon begins from the Motive identification (see below).
+Despite the fact that the clue "The Candlestick was in the Trophy Room at 12:00 AM if and only if a suspect motivated by Pride was in the Lounge at 11:45 PM." in general is proven to be difficult for the agents to follow correctly, by having locked the Pride Motive on Mrs White the "if and only if" becomes easier to follow and determine the Candlestick as the Weapon. The failure is to determine that Mrs White was in the Lounge at 11:45 PM.</t>
+    </r>
+  </si>
+  <si>
+    <t>GENERAL AGENTS BEHAVIOUR AND CONSISTENT FAILED QUESTIONS PER CASE ANALYSIS</t>
+  </si>
+  <si>
+    <t>For reference I also have the correct answer per case.</t>
+  </si>
+  <si>
+    <t>The Auditor challenged the Detective on run 5, corrected the WEAPON (Horseshoe --&gt; Lead Pipe) but changed to wrong murderer (Mrs. Peacock --&gt; Colonel Mustard).
+Also changed (wrong to wrong) C, F, G, H</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question C (WHERE)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Since the agents found the murder happened at 12:00 (correctly chosen on all runs), the weapon must be in the murder room at that time. So the clue "The murder weapon was in the Billiard Room at 12:00 AM OR Mrs. Peacock was in the Dining Room at 11:00 PM." proves the first half of the OR is correct. However the agents struggle to follow both paths.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Question F (MONSIEUR BRUNETTE LOCATION)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Based on the clue "The Poison was in the room just east of Monsieur Brunette at 12:00 AM." the location could be defined easily by using the map from Forensics (if Poison is at [x,y] we must find [x-1,y]). However the starting position of Monsieur Brunette was difficult to be determined by the clue "Monsieur Brunette was in the Study at 11:00 PM if and only if the Wrench was in the Lounge at 11:00 PM.".</t>
+    </r>
+  </si>
+  <si>
+    <t>In some cases the agents responded in Chinese (???)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Question H (MRS WHITE @11.00 PM LOCATION)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The main clue for this is "Mrs. White was in the Dining Room at 11:00 PM OR the Poison was in the Studio at 11:00 PM.". The Agents failed to follow the correct path. They chose "Mrs. White was in the Dining Room at 11:00 PM" which led to wrong hypotthesis.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Auditor found physical violations by using the json map and tha manhattan distance rule, but failed to re-evaluate the logical assumptions most of the times</t>
+  </si>
+  <si>
+    <t>In all cases the Agents mostly failed to follow clues that included "if and only if" and "OR" conditions. They most propably took a guess on which is correct or chose by being biased by other clues</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +677,32 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -268,12 +730,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -591,17 +1062,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3748830A-B28B-4F54-9596-6D91485AA2CB}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,7 +1092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1052</v>
       </c>
@@ -641,7 +1112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1182</v>
       </c>
@@ -661,7 +1132,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1230</v>
       </c>
@@ -681,7 +1152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2145</v>
       </c>
@@ -701,7 +1172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2176</v>
       </c>
@@ -721,7 +1192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2279</v>
       </c>
@@ -741,7 +1212,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>2372</v>
       </c>
@@ -761,7 +1232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2680</v>
       </c>
@@ -781,7 +1252,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2799</v>
       </c>
@@ -801,7 +1272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2973</v>
       </c>
@@ -828,305 +1299,309 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6E4106-5CC9-44AD-AC20-27CF18A53C82}">
-  <dimension ref="A1:B74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:B73"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="158.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="174.44140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1052</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.35">
+      <c r="B2" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="80" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>1182</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1"/>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="80" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>1052</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>1182</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>1230</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B31" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>2145</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B35" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B37" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B38" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>2176</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B42" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>1230</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="1"/>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="1"/>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B23" t="s">
+    <row r="43" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="B43" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B44" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="80" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="B25" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="80" x14ac:dyDescent="0.2">
-      <c r="B26" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="B27" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>2145</v>
-      </c>
-      <c r="B30" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <v>2176</v>
-      </c>
-      <c r="B39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>2279</v>
       </c>
-      <c r="B47" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B47" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B48" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="B49" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B51" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="5"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>2372</v>
       </c>
-      <c r="B54" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="1"/>
-      <c r="B55" t="s">
+      <c r="B54" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B55" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B56" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B57" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B58" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B59" s="5"/>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>2680</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" s="1">
+        <v>2799</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1">
+        <v>2973</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B73" s="4" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="1"/>
-      <c r="B56" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B57" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="1">
-        <v>2680</v>
-      </c>
-      <c r="B62" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="1"/>
-      <c r="B63" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="1"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="1">
-        <v>2799</v>
-      </c>
-      <c r="B67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="1"/>
-      <c r="B68" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="1">
-        <v>2973</v>
-      </c>
-      <c r="B72" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="1"/>
-      <c r="B73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B74" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
